--- a/协作/07-需求契约.xlsx
+++ b/协作/07-需求契约.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>高</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -608,15 +608,79 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-18 01:15:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>契约-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>验收-0005</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>协议默认全角色全开、零配置，本仓库 37 份编号交付物 + 3 份附件清单全部在档</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>已批准</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>契约-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>验收-0006</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>对外交付包 v3.5 可交付，且归档快照可校验、可还原</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>已批准</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="E2:E121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"已批准,驳回"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/07-需求契约.xlsx
+++ b/协作/07-需求契约.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -672,6 +672,38 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>契约-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>验收-0008</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DCG 版本库不含协议与模板：TEAMODEL.md、协作/模板/**、docs/TEAMODEL_draft_v1.md 已移除；引用登记在 01 项目画像与 13 文件所有权</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>已批准</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:40:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/07-需求契约.xlsx
+++ b/协作/07-需求契约.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -704,6 +704,38 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-18 03:40:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>契约-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>验收-0009</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>README 标题为 # DCG、不含「v2 是单产物编译器…不保证兼容」段、§0 为适配场景（含适合/不适合两张表）</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>已批准</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:10:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/07-需求契约.xlsx
+++ b/协作/07-需求契约.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -736,6 +736,38 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18 04:10:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>契约-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>验收-0010</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>README 开篇写明 JSONata 是结构描述语言、编译成固化 Python；§0 主场景为任意数据结构转换（0.1 首行单列该场景）；不含「v2 是单产物编译器」段</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>已批准</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:30:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/07-需求契约.xlsx
+++ b/协作/07-需求契约.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -768,6 +768,38 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-18 04:30:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>契约-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>验收-0011</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>README 不含「当前实测/引擎修订锚点/§6 性能终值锚定」段；§0 只有标题与主场景说明，不含 0.1/0.2/0.3 子节；其他章节未受影响</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>已批准</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:50:00 +08:00</t>
         </is>
       </c>
     </row>
